--- a/excel/pacifico-dex-sociedad-anonima-cerrada_ruta_proxima_semana.xlsx
+++ b/excel/pacifico-dex-sociedad-anonima-cerrada_ruta_proxima_semana.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rutas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rutas'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rutas'!$A$1:$J$145</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -57,11 +57,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,19 +428,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,8 +495,7496 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>C001493785</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>21434507</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>QUISPE DE HUANCAHUARI CLARA TEODULA</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>AV. MAURTUA NRO. 267 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>C001384828</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>10411072113</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MIRANDA TOLEDANO MARITZA VILMA</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>CL. CAJAMARCA NRO. 316 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>C001364470</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10214280928</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>NU EZ TATAJE DE DIAZ MARIA LUISA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>LA MAR NRO. 354 INT. 5 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>C001494757</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21441340</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>MENDIETA OLARTE VDA DE LUJAN OCTAVIA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>CL. LA MAR NRO. 515 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>C001476915</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21564967</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HERNANDEZ TORRES CARLOS CESAR</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>PARADA HUANCAVELICA PTO NRO. 7 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>C001419292</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>45298394</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>QUISPE MANTARI CLAUDIA KARINA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>MCDO. HUANCAVELICA S/N Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>C004030178</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>80017595</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LEON SEGURA CARMEN PATRICIA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>BOTIJERIA ANGULO NORTE C-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>C004175753</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>74375244</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>LEDESMA ANYOSA TRILLCE ELLYANA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>BOTIJERIA ANGULO NORTE Mz. E LT.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>C001374919</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>30833340</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ARENAS ROJAS MARIA DEL PILAR</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>CL. LIMA NRO. 824 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>C000880980</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10215460555</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>CHOQUE OLIVARES ROSARIO RUTH</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>AV. MER CARLOS RAMOS LOAYZA P49 MZA. MAZAA280 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>C004253017</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>40192544</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>GAVILAN BENDEZU LIZ CATHERINE</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>MCDO CARLOS RAMOS LOAYZA PTO 20 (REF FRENTE A SAUL AYALA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>C001016040</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>46947461</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>QUISPE CONISLLA GUSTAVO ALONSO</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>MCDO RAMOS LOAYZA MZA. 036 PSTO. 16 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>C001174602</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>28820094</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ANYOSA CALDERON MAXIMINA TERESA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>CL. MANUEL MEDINA NRO. 501 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>C001714600</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>70248759</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>RAMOS ALTAMIRANO FRESCIA GERALDINE</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>BOTIJERIA ANGULO SUR 7 MZ: R L NRO. 7 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>C004250372</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>76201929</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>CAMPOS CALDERON JOSSEPH ALEXIS</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Mdo Modelo plataforma Pto 204</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>C000880985</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>10214066349</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>CHANG PURILLA JOSE FELIX</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>AV. MER MODELO DE ICA P79 MZA. MAZAA250 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>C001540587</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>10214309136</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HUAMAN HUAYANCA ROSA ELENA </t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>PJ NUEVA ESPERANZA C - NRO. 12 Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>C001565392</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>46504360</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>MENDRAGON APAZA VIRGINIA TERESA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>PJE. NUEVA ESPERANZA C NRO. 15 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C001492920</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>43048255</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>HUAMAN ROJAS CYNTHIA LUZ</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>AV. SEBASTIAN BARRANCA D NRO. 1 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C001462885</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>10214296531</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>PALACIOS SIGUAS ROSARIO ARACELLI</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>URB SANTA MARIA F - NRO. 13 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C001161289</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>21438974</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>CUCHO DE LA CRUZ RAQUEL ESPERANZA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>AV. MDO ARENALES NRO. 9 PSTO. K-9 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>C004008546</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>76244129</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>CORONADO LOPEZ PATRICK VICTOR</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>MERCADO STO DOMINGO PUESTO A1 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>C001752397</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>45494868</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>CACERES QUICAÑO NOEMY LIZBETH</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>MCDO. MRCD ARENALES SECTOR 1 PUESTO NRO. E3 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>C000882668</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>20119149</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>CLAUDIO TORRES VIVIANA</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>AV. MER MERCADO ARENALES PS/N MZA. MAZAA001 URB. MERCADO ARENALES Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>C004235629</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>10296506864</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>FALCON CHALCO JUAN JOSE</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>AV. JUAN DE LOYOLA 376 ICA-ICA.ICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>C001752245</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>44444485</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>RAMOS SIVIRICHI CYNTHIA LIZ</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>SANTA ROSA MZ E LOTE NRO. 4 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>C001563527</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>41071491</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>MINAYA RIOS DE MOGOLLON JESSICA VANESA</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>AAHHSANTA ROSA DE LIMA NRO. 15 LOTE. I URB. AL FRENTE DE LA PANADERIA Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>C001405735</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>10214545468</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>GARCIA VILLANUEVA BETTY MERCEDES</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>STA ROSA DE LIMA F  NRO. 39 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>C001616610</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>40559324</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>LENGUA LOVERA MARINA DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>AV. SANTA ROSA DE LIMA MZ A NRO. 6 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>C001103760</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>10215640995</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BARRIGA LUQUE DE CARO ELSA NERY </t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>SANTA ROSA DE LIMA MZ G LT NRO. 11 Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>C001551423</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>76667629</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>MATA CUPE DYLAN RENATO</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>SANTA ROSA DE LIMA K NRO. 19 URB. COSTADO DE MALQUI CCENCHO Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>C001547857</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>10420655521</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>MALQUI CCENCHO MARIA KATIA</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>AAHH PASAJE SANTA ROSA K - NRO. 17 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>C000872408</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>10214698035</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CORDOVA AGUILAR FAUSTA </t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>PJE. PASAJE SANTA ROSA DE LIMA NRO. L - 1 Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>C000872287</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>10162922225</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LARA SALAZAR ISABEL </t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>AV. OTR  M-F L-14 MZA. MAZAA390 LOTE. 14 URB. PJ SE OR DE LOS MILAGROS Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>C001708107</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>43769057</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>COELLO TINEO TONY WILLIANS</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>PPJJ SEÑOR DE LOS MILAGROS MZ NRO. 12 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>C001708345</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>10214898425</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESCATE HERNANDEZ MALENA HAYDE </t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>AAHH SEÑOR DE LOS MILAGROS MZ NRO. 03 Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>C000882032</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>10214248901</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>GUTIERREZ ROJAS TEODORO</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>AV. OTR PJ SRDE LOS MILAGROS M- MZA. MAZAA18A LOTE. 4 URB. SR DE LOS MILAGROS Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>C001330257</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>21425611</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>GALLEGOS CUBA LUPE MARTHA</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>JR. SE OR DE LOS MILAGROS MZA. D LOTE. 3 URB. SE OR DE LUREN Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>C004060670</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>73135005</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>CARRASCAL PEVE MELISSA JACKELINE</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>P.j.sr Los Milagros  B4 arenales, 110101 Ica, Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>C001549391</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>21547517</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>MALCA CALVERA PAMELA GEOVANNA</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>URBEL CARMEN II-ETAPA NRO. 11 INT. I URB. PASANDA LUPE GALLEGOS Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>C001516381</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>45502294</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>YARMA ECHACCAYA GISSELA</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>AV. PJ SRD LOS MILAGROS A- NRO. 10 Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>C001453033</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>21521331</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>YALLE CALDERON EDITH MIRIAM</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>URBSAN JOAQUIN T- NRO. 2 URB. II ETAPA Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>C000875789</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>21474216</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>PAREDES CONDORI NEMIA ELENA</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>AV. MER SAN ANTONIO NRO. P-461 MZA. MAZAA360 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>C001500991</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>21443854</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ANYOSA HERNANDEZ ROSA HAYDEE</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>AV. MERCADO SAN ANTONIO NRO. 440 URB. MERCADO SAN ANTONIO Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>C004061770</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>10437301072</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>BANDA ATOCCSA JUAN DIEGO</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>MCDO SAN ANTONIO PSTO NRO 495 - ICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>C004054145</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>22071408</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>REYNOSO ROMERO EDITA</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>MCDO SAN ANTONIO PTO 59 SAN JOAQUIN - ICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>C004142370</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>21544989</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ORELLANA MORON SONIA BEATRIZ</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>MERCADO SAN ANTONIO PUESTO NRO 442</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>C001572913</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>74903551</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>CCAYCO CANALES MARISA</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>MCDO. SAN ANTONIO PTO NRO. 9 URB. FRENTE A CALIN Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>C001112418</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>21452064</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>MUNOZ DE BONIFAZ BERTHA ELIZABETH</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>SAN JOAQUIN VIEJO STA ROSA NRO. 302 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>C004033260</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>47765342</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>BERNAOLA AYQUIPA RENZO JESUS</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>AV GRAU N4 SAN JOAQUIN VIEJO - ICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>C004196959</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>6604628</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>SARAVIA HERNANDEZ LEONOR JESUS</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>SAN JOAQUIN VIEJO 609 ICA-ICA-ICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>C000875877</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>10215603283</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>ROJAS CALISAYA BENEDICTA</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>SAN JAOQUIN VIEJO LOTE. 17 URB. COOP NUEVA ESPERANZA Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>C004216983</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>43773369</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>SANCHEZ MENDOZA ERNESTO</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Urb. SAN JOAQUIN NUEVO 3ER ETP. Mz. Q Lt. 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>C004142368</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>21440827</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>GOMEZ DE HUASASQUICHE BRIGIDA</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>URB SAN JOAQUIN 4TA ETAPA MZ. I LT. 26 ICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>C001715909</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>10215681314</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>MORON GARCIA IRMA CONSUELO</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>ASOC OSCAR SANCHEZ DULANTO MZ NRO. 03 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>C004033257</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>21553787</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>PARIONA GARAYAR DORIS GLORIA</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>OSCAR SANCHEZ MZ G 17 - ICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>C004193312</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>9425585</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>SACHA DIAZ CARMEN DARIA</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>AAHH. KEIKO B-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>C001028351</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>10233683</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>CHECNES JANAMPA MAGDALENA</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>ASOC OSCAR SANCHEZ DULANTO NRO. 7 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>C001649992</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>21556332</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>JANAMPA TAQUIRI MAGDA ELIZABETH</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>AU. AAHH KEIKO SOFIA Ñ1 NRO. 1 Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>C001751961</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>21431061</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>GARCIA CRUZ MELANIA DE JESUS</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>JOSÉ OLIVA RASSETO A NRO. 19 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>C004216295</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>8442030</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TENORIO HUAMANI GLORIA MARTHA </t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>ASOCIACION KEIKO SOFIA Mz. J Lt. 6, 110101 Ica, Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>C001535863</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>40914034</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>YALLICO ALFARO MARLENY NELY</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>KEIKO SOFIA FUJIMORI J NRO. 1 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>C001417713</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>21574727</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROJAS GONZALES EDITMAN SUSAN </t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>OSCAR SANCHEZ DULANTO C NRO. 5 Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>C001535865</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>40855900</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>NANAJUARI CALDERON HILDA YOVANA</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>LA VICTORIASAN JOAQUIN VIEJO NRO. 11 URB. 1/2 CDRA D CLIENTE-ALVITEZ Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>C004216297</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>21520018</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>SALAS HUAMANI JUANA</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>CAMINO REAL Mz. B Lt. 8 2DA ETP LA VICTORIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>C004033254</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>42249542</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TORRES AQUIJE CYNTHIA ELIZABETH </t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>LA VICTORIA 320 FRENTE AL SEMINARIO - ICA, 110101 Ica, Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>C004016419</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>21492980</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>ALEJOS QUISPE HAYDEE CONSUELO</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>LOS ESPINOS E-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>C004020448</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>21569834</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARDENAS MONTAÑO SANDRA KARIN </t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>PJ VIRGEN DEL CARMEN D-5, 110101 Ica, Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>C004020449</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>41063320</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEJIA AQUIJE YOLANDA CECILIA </t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>PJ VIRGEN DEL CARMEN C-15, 110101 Ica, Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>C004020428</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>45921300</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>RIVERA CONDORI ERIK</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>AV PRINCIPAL COMATRANA N-49</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>C001568846</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>21520876</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>AYBAR GUERRA JESUS ALFONSO</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>AV. PRINCIPAL COMATRANA K NRO. 24 URB. FRENE COLEGIO JOSE OLAYA Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>C004020425</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>46789824</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>CARBAJO MORALES ALBERTO LUIS</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>AV PRINCIPAL COMATRANA H-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>C004101290</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>70955343</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>RAMOS DELGADO MAURA ALEJANDRA</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>URB MENORCA POSADA DEL SOL MZ C8 LT. 05 ICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>C001372283</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>10457631435</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>PAUCAR GUTIERREZ ERIKA RUTH</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>BARRIO SAN MARTIN  MZ B LT NRO. 01 URB. AAHH ALBERTO FUJIMORI Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>C001423201</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>43785574</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>SALAZAR HUACCACHI ANDREA YAQUELYN</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>ALBERTO FUJIMORI H NRO. 8 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>C001623767</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>45667235</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>GARCIA MAMANI YOVA</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>AAHH ALBERTO FUJIMORI MZ H LT NRO. 2 Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>C001198539</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>42395148</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>TACAS HUANCAHUARI MIRIAM</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>PPJJ SR DE LUREN D- NRO. 8 URB. 4TA ETAPA Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>C004176366</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>21534095</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>ARAUJO TORRES DE LAGOS ELSA</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>PUEBLO JOVEN 5TA ETAPA C - 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>C004200754</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>21435997</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>FARFAN DE MORON CARMEN GLORIA</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>PPJJ SRDE LUREN MZ F LT NRO. 32 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>C001568416</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>10214359974</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FARFAN DE MORON CARMEN GLORIA </t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>PPJJ SRDE LUREN MZ F LT NRO. 32 Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>C000882686</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>21561203</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>SIERRA ESPINOZA VICTORIA JAZMIN</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>JR. AAHH SE OR DE LUREN II ETAPA NRO. 260 LOTE. 14 URB. SE OR DE LUREN Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>C004029978</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>10215295295</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>LLAMOCCA ATAUJE DORA</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>AAHH SEÑOR DE LUREN 2DA ETAPA B-28 FRENTE COMISARIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>C001532013</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>10214103431</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>BACILIO JORGE MARIANO</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>PPJJ SR DE LUREN 2 ETAPA MZ NRO. 07 Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>C001547525</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>47244282</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>QUISPE HUAYTA PERCY</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>URB TEMISTLOTE ROCHA P- NRO. 12 URB. DONDE QUISPE MANCCO DENIS Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>C001346898</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>10215333375</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>PALOMINO APCHO ELIZABETH MARLENI</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>AV. PJ SR DE LUREN MZA C - LOT NRO. 13 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>C001373802</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>21424416</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>QUISPE DE SAMATA TEODORA</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>TEMISTOCLES ROCHA P NRO. 4 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>C004183040</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>76467604</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MALLQUI PAUCAR MARYCARMEN </t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>PPJJ SR.DE LUREN / NUEVA UNION B-14, 110101 Ica, Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>C001623768</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>21532363</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>QUISPE ONCEBAY JUANA LILIANA</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>TEPRO ALTO SAN MARTIN MZ D LT NRO. 28 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>C001492218</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>21441512</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUTIERREZ QUISPE GELACIO </t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>SIMON BOLIVAR A NRO. 7 URB. CASERIO SAN MARTIN Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>C004003306</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>21532334</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>QUISPE ESPINO OSCAR NICOLAS</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>CASERIO SAN MARTIN L - 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>C001548489</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>44535864</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HUAYANCA PILLACA JAIME JOSE </t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>CASERIO SAN MARTIN DE PORRAS NRO. 13 URB. FRENTE A LA PLAZUELA Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>C001761938</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>21407361</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>GARAYAR BERNALES CARMEN LUZ</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>CASERIO SAN MARTIN  AV JORGE NRO. L - 17 Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>C004042769</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>10214220259</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>JUNES ARROYO LUZ HAYDEE</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>CASERIO SAN MARTIN D-20, 110101 Ica, Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>C004239543</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>10485481350</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUISPE SAYRITUPAC KATERINE YOANA </t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>CASERIO SAN MARTIN DE PORRAS Mz. c Lt. 14, 110101 Ica, Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>C000872204</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>10214567631</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>SOTO PAREDES PAULINA</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>AV. AVE CHAVEZ JORGE MW L10 MZA. MAZAA110 LOTE. 10 URB. CASERIO SAN MARTIN Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>C001752252</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>40732814</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>ALCA CUSI VILIA</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>POSADA DEL SOL MZ A LOTE NRO. 34 Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>C004237308</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>41836151</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>RAMOS VIVANCO ELIZABETH</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>VILLA LOS EDUCADORES M-29, 110101 Ica, Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>C001708342</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>10215516798</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MONTAÑO FLORES NELLY MELIANA </t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>AAHH LAS DUNAS MZ G LT NRO. 01 Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>C004033253</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>75929210</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CUCHO BENDEZU RONY </t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>URB LAS DUNAS D-10 ENTRADA COLEGIO PASTORCITO - ICA, 110101 Ica, Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>C004036835</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>21559914</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>QUISPE FLORES LUIS OCTAVIO</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>URB SAN JOAQUIN 1° ET A-26, 110101 Ica, Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>C000872050</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>21407489</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>FALCONI ARAUJO EDUARDA ELIZABETH</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>URB SAN JOAQUIN A NRO. 12 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>C001518190</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>10415547141</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CANCHO ROJAS JUDITH GRISELDA </t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>SAN JOAQUIN I  NRO. 01 URB. LAS DUNAS Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>C000872048</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>10214159878</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>BAUTISTA SOTO JUAN FELIX</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>MAL. PSJ OASIS MG L11 MZA. MAZAA110 LOTE. 11 URB. URB LAS DUNAS Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>C001708619</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>21416600</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>LEGUA REYES LUCIA YVONE</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>URB SAN JOAQUIN K  NRO. 16 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>C000881327</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>10214348239</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REVILLA LARA ASUNCION LUIS </t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>AV. OTR URBSAN JOAQUIN M-G L-24 MZA. MAZAA020 LOTE. 24 URB. SAN JOAQUIN II ETAPA Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>C001218188</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>10214605754</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REVILLA LARA JOSE LUIS </t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>III ETAPA MZA. R LOTE. 10 URB. SAN JOAQUIN Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>C004041142</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>41918865</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>HUAMAN BERROCAL GLORIA ROSARIO</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>URBSAN JOAQUIN I-ETAPA G- NRO. 21 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>C001477306</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>45964685</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>ALTAMIRANO ESTACIO MIRIAM SALOME</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>URB EL CARMEN A- NRO. 4 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>C001546985</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>47888086</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>CUSIHUALLPA CHACMA JHANET NATHALY</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>URB VILLA LOS EDUCADORES Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>C001397985</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>10751151</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>HUARCAYA TACAS RENEE</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>AV. VILLA EDUCADORES A NRO. 7 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>C000872186</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>21452594</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CUAREZ PICHIHUA CONSTANTINA DAMIANA </t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>AV. OTR SR DE LUREN M-J L-11 NRO. J-11 MZA. MAZAA940 LOTE. 11 URB. 1 ETAPA Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>C004196945</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>21569254</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>JALIXTO MALDONADO ERIKA BEATRIZ</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>PPJJ. SR. DE LUREN J-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>C001538829</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>10214237640</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>PAUCAR ANTONIO JULIO MAXIMO</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>PJ SEÑOR DE LUREN I-ETAPA C NRO. 1 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>C004193305</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>21465851</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>LOPEZ ANGULO JULIA ROSA</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>AV. MELCHORITA B-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>C001573535</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>15430778</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>MEZA FLORES SONIA ANGELICA</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>AV. MELCHORITA  PJ SEÑOR DE LUREN NRO. 12 MZA. A Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>C001494214</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>43752531</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>RUIZ VEGA GROBER</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>PJE. SR DE LUREN M- NRO. 6 URB. FTE ARIMANA Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>C004044931</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>48658559</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>ALFARO MITACC ANTHONY</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>AV. JOSE SALAS M-6 PPJJ SR DE LUREN - ICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>C001484180</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>10417603943</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>CUYA VEGA PAULINA</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>AV. INDUSTRIAL MZA. G LOTE. 17 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>C001397980</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>21417961</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUISPE MARTINEZ LUCIANO </t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>AV. PJ SR DE LUREN G- NRO. 13 URB. I ETAPA- COSTADO DE ARIMANA Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>C001466390</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>10214395270</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAUTISTA BENAVIDES EDELFINA GENOVEVA </t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>AV. INDUSTRIAL MZA. G LOTE. 11 Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>C004251011</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>47572376</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>PARRA ESPINO INGRID JACKELIN</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>PROGRAMA MUNICIPAL 4TA ETP. G-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>C000875868</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>10214210636</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SURICHAQUI TORREALVA DE CLARA </t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>AV. OTR 4 ETAPA/PROGRMUNICIPAL M- MZA. MAZAA200 LOTE. 8 URB. URB SAN JOAQUIN ETP 4 Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>C001738539</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>21462040</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GASTELLO ARANGO SILVIA ELDELISA </t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>URB SAN JOAQUIN 1ERA ETAPA Y2 NRO. 2 Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>C001511937</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>10702804529</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDINA ARQUIÑEGO ASHLYE BELEN </t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>AV. JOSE MARIA EGUREN NRO. 204A Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>C004039549</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>41191786</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>GODOY CONDORI ELEAZAR FREDY</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>AV. OTR SAN JOAQUIN MX2 LT NRO. 10 LOTE. 10 URB. I ETAPA Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>C001508200</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>10215276134</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEON DIAZ WUENDY MIRIAN ANGELICA </t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>IV ETAPA MZA. J LOTE. 03 Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>C001736282</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>40896964</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>REYES GUARACHA JACQUELINE ROCIO</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>URB SAN JOAQUIN 1ERA ETAPA NRO. T-22 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>C001376381</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>10214439692</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>CAMPOS HUALLPA DIONICIO</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>SAN JOAQUIN T  NRO. 10 Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>C001536840</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>70280454</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDINA ARQUIÑEGO CHARLIE FABIAN SLIM </t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>JOSE MARIA EGUREN NRO. 204 Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>C001734421</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>21574883</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ASCAMA RAMOS DORA ALVINA </t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>URB SAN JOAQUIN 1ERA ETAPA MZ NRO. 23 Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>C001579130</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>22252704</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>CHILQUILLO ANAGUARI GUILLERMO PROSPERO</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>MCDO. 28 DE JULIO PSTO. 59 Y 6 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>C001708109</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>40441132</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>AYQUIPA PENA LUISA ANABEL</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>AV. MER COOP 28 DE JULIO MZ Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>C001492103</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>21412541</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>ALFARO CRUZ MARGARITA LUCILA</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>MCDO. MCDO MUNICIPAL PTO NRO. 38 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>C001460089</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>10214363491</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>APARCANA REJAS WILFREDO EMILIO</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>MCDO. CENTRAL B NRO. 16 URB. 28 DE JULIO -SAN JOAQUIN Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>C001622306</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>71966779</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>ANTEZANA ARONI ANTHONY PATRICK</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>MCDO. MERCADO 28 JULIO NRO. 6 Ica-Ica-Ica</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>C004048227</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>76982687</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>ARONE ALLCCA MARTHA BETSABE</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>AV. JOSE MATIAS EGUREN 134</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>C001705082</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>21554215</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>REYES CASTRO LISSET KARIM ESTELA</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>URB SAN JOAQUIN - EL GUAYABO NRO. 11 Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>C004216293</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>41561591</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>VELASQUEZ CERON VICTOR RAUL</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>EL GUAYABO RICARDO PALMA A-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>C004036838</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>40857052</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANCHEZ LANDEO NORA ESTELA </t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>EL GUAYABO RICARDO PALMA A-1, 110101 Ica, Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>C004036837</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>5937356</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>VASQUEZ HIDALGO MARITZA FLORENTINA</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>EL GUAYABO E-22, 110101 Ica, Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>C004060667</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>46778243</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARBAJAL ROMERO THATIA </t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>SAN JOAQUÍN MZ-X1 LT-26, 110101 Ica, Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>C001112453</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>10214036580</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CRUZ ALEGRIA ISAAC ADOLFO </t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>AV. JOSE MARIA EGUREN NRO. 283 Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>C001507663</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>46567757</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FELIPA MORON ANDREA CECILIA </t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>CL. FRAY RAMON ROJAS MZ B LT NRO. 23 URB. ESPALDA DE TRUJILLO YANINA Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>C001624618</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>10221898171</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORMEÑO DE GARCIA MARIA MARGARITA </t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Ica (Ica)</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>AV. LA VICTORIA NRO. 1090 Ica-Ica-Ica, 110101 Ica, Perú</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:J145"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>